--- a/Document/LLC/LLC.xlsx
+++ b/Document/LLC/LLC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\PowerrToplogyStudy\PowerToplogyStudy\Document\LLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CAFB94-65A6-4139-8AD9-AC34977C53AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E0512B-DABF-429E-86F7-FB4038850D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,17 +16,28 @@
     <sheet name="FullBridgeLLC" sheetId="1" r:id="rId1"/>
     <sheet name="HalfBridgeLLC" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>1.初级LV_PWM1A LV_PWM2B导通次级对应的Q6Q14导通</t>
   </si>
@@ -38,16 +49,54 @@
   </si>
   <si>
     <t>3.初级LV_PWM1A LV_PWM2B导通次级对应的Q5Q11导通</t>
+  </si>
+  <si>
+    <t>Q1/Q4导通、Q2/Q3关断时，励磁电流的路径为电源→Q1→Cr→Lr→Lm→Q4→电源，此时Cr充电。当Lr和Cr的谐振结束后，进入Mode ②。</t>
+  </si>
+  <si>
+    <t>Mode1</t>
+  </si>
+  <si>
+    <t>Mode2</t>
+  </si>
+  <si>
+    <t>Mode3</t>
+  </si>
+  <si>
+    <t>为了防止Q1/Q3和Q2/Q4同时导通（此时LLC相当于短路，大电流会烧坏MOSFET），在切换Leg的时候会特意设置一个延迟时间，这就是死区时间(Deadtime)，此时4个MOSFET均关断。在这期间，C1和C4开始充电，Vds1和Vds4升高；C2和C3开始放电，Vds2和Vds3下降。当C1~C4的充放电完成后，Vds1和Vds4升至电源电压，而Vds2和Vds3降至0V,当Q2/Q3导通时Vds2/Vds3均为0V，所以这是ZVS，MOS管实现软开.</t>
+  </si>
+  <si>
+    <t>Q2/Q3导通、Q1/Q4关断时，励磁电流的路径为电源→Q3→Lr→Lm→Cr→Q4→电源，此时Cr放电。当Lr和Cr的谐振结束后，进入Mode 4。</t>
+  </si>
+  <si>
+    <t>Mode4</t>
+  </si>
+  <si>
+    <t>为了防止Q1/Q3和Q2/Q4同时导通（此时LLC相当于短路，大电流会烧坏MOSFET），在切换Leg的时候会特意设置一个延迟时间，这就是死区时间(Deadtime)，此时4个MOSFET均关断。在这期间，C2和C3开始充电，Vds2和Vds3升高；C1和C4开始放电，Vds1和Vds4下降。当C1~C4的充放电完成后，Vds2和Vds3升至电源电压，而Vds1和Vds4降至0V,当Q2/Q3导通时Vds1/Vds4均为0V，所以这是ZVS，MOS管实现软开.</t>
+  </si>
+  <si>
+    <t>reference link</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/c_1469297405468684288</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -70,13 +119,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -236,8 +300,8 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>458032</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>91686</xdr:rowOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>145474</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -281,7 +345,7 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>358963</xdr:colOff>
       <xdr:row>94</xdr:row>
-      <xdr:rowOff>167892</xdr:rowOff>
+      <xdr:rowOff>167893</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -350,6 +414,50 @@
         <a:xfrm>
           <a:off x="11582400" y="4023360"/>
           <a:ext cx="3932261" cy="6104149"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>496188</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>18372</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9B6B841-322B-31F5-2C2A-F1E780655E20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10972800" y="13812982"/>
+          <a:ext cx="10249788" cy="4160881"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -624,32 +732,155 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="Q1:Q4"/>
+  <dimension ref="Q1:AG66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="17:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="17:28" x14ac:dyDescent="0.3">
       <c r="Q1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Z1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="17:28" x14ac:dyDescent="0.3">
       <c r="Q2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="17:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="17:28" x14ac:dyDescent="0.3">
       <c r="Q3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="17:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="17:28" x14ac:dyDescent="0.3">
       <c r="Q4" t="s">
         <v>2</v>
       </c>
     </row>
+    <row r="60" spans="19:33" x14ac:dyDescent="0.3">
+      <c r="S60" t="s">
+        <v>5</v>
+      </c>
+      <c r="T60" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="19:33" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U61" s="3"/>
+      <c r="V61" s="3"/>
+      <c r="W61" s="3"/>
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3"/>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
+      <c r="AB61" s="3"/>
+      <c r="AC61" s="3"/>
+      <c r="AD61" s="3"/>
+      <c r="AE61" s="3"/>
+      <c r="AF61" s="3"/>
+      <c r="AG61" s="3"/>
+    </row>
+    <row r="62" spans="19:33" x14ac:dyDescent="0.3">
+      <c r="S62" t="s">
+        <v>7</v>
+      </c>
+      <c r="T62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="19:33" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S63" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="T63" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="U63" s="4"/>
+      <c r="V63" s="4"/>
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="4"/>
+      <c r="AA63" s="4"/>
+      <c r="AB63" s="4"/>
+      <c r="AC63" s="4"/>
+      <c r="AD63" s="4"/>
+      <c r="AE63" s="4"/>
+      <c r="AF63" s="4"/>
+      <c r="AG63" s="4"/>
+    </row>
+    <row r="64" spans="19:33" x14ac:dyDescent="0.3">
+      <c r="S64" s="5"/>
+      <c r="T64" s="4"/>
+      <c r="U64" s="4"/>
+      <c r="V64" s="4"/>
+      <c r="W64" s="4"/>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="4"/>
+      <c r="AA64" s="4"/>
+      <c r="AB64" s="4"/>
+      <c r="AC64" s="4"/>
+      <c r="AD64" s="4"/>
+      <c r="AE64" s="4"/>
+      <c r="AF64" s="4"/>
+      <c r="AG64" s="4"/>
+    </row>
+    <row r="65" spans="19:33" x14ac:dyDescent="0.3">
+      <c r="S65" s="5"/>
+      <c r="T65" s="4"/>
+      <c r="U65" s="4"/>
+      <c r="V65" s="4"/>
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+      <c r="AA65" s="4"/>
+      <c r="AB65" s="4"/>
+      <c r="AC65" s="4"/>
+      <c r="AD65" s="4"/>
+      <c r="AE65" s="4"/>
+      <c r="AF65" s="4"/>
+      <c r="AG65" s="4"/>
+    </row>
+    <row r="66" spans="19:33" x14ac:dyDescent="0.3">
+      <c r="S66" s="5"/>
+      <c r="T66" s="4"/>
+      <c r="U66" s="4"/>
+      <c r="V66" s="4"/>
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+      <c r="AA66" s="4"/>
+      <c r="AB66" s="4"/>
+      <c r="AC66" s="4"/>
+      <c r="AD66" s="4"/>
+      <c r="AE66" s="4"/>
+      <c r="AF66" s="4"/>
+      <c r="AG66" s="4"/>
+    </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="T61:AG61"/>
+    <mergeCell ref="T63:AG66"/>
+    <mergeCell ref="S63:S66"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="AB1" r:id="rId1" xr:uid="{4875D38A-96FD-44B6-B598-70E2A366C78E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
